--- a/server/excel/release/cross-ingot-ranking.xlsx
+++ b/server/excel/release/cross-ingot-ranking.xlsx
@@ -60,7 +60,7 @@
     <t xml:space="preserve">开启等级</t>
   </si>
   <si>
-    <t xml:space="preserve">Vượt phục Nguyên bảo tiêu hao xếp hạng</t>
+    <t xml:space="preserve">Vượt phục Kim cương tiêu hao xếp hạng</t>
   </si>
   <si>
     <t xml:space="preserve">2024-07-15 00:00:00</t>
